--- a/samples/example_plan.xlsx
+++ b/samples/example_plan.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -436,8 +436,9 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,15 +489,20 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>статус</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>критический путь</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>запас, дн</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>прогресс, %</t>
         </is>
@@ -540,14 +546,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>готова</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>да</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
       <c r="L2" t="n">
         <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -592,14 +603,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>в работе</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>да</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
       <c r="L3" t="n">
         <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -642,11 +658,16 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>заблокирована</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
         <v>11</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -692,13 +713,18 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>не начата</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>да</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -744,13 +770,18 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>не начата</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>да</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -794,11 +825,16 @@
           <t>2027-01-08</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>не начата</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
         <v>8</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -842,11 +878,16 @@
           <t>2027-01-05</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>не начата</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -892,13 +933,18 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>не начата</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>да</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -944,13 +990,18 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>не начата</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>да</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -996,13 +1047,18 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>не начата</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>да</t>
         </is>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1048,13 +1104,18 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>не начата</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>да</t>
         </is>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1100,13 +1161,18 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>не начата</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>да</t>
         </is>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>0</v>
       </c>
     </row>
